--- a/Configs/GameConfig/Datas/HeroLevelConfig.xlsx
+++ b/Configs/GameConfig/Datas/HeroLevelConfig.xlsx
@@ -2,39 +2,375 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25600" windowHeight="12080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="21">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +378,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1029,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -414,7 +1039,14 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E60"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col width="8.54545454545454" customWidth="1" min="1" max="1"/>
+    <col width="11.8181818181818" customWidth="1" min="2" max="2"/>
+    <col width="7.54545454545455" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="34.2727272727273" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/Configs/GameConfig/Datas/HeroLevelConfig.xlsx
+++ b/Configs/GameConfig/Datas/HeroLevelConfig.xlsx
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>升到下一级所需经验(旧 max_exp)</t>
+          <t>升下一级所需经验，最高等级填0（旧 max_exp，封顶55级）</t>
         </is>
       </c>
     </row>
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>该级升下一级所需经验</t>
+          <t>最高等级，不再获取经验</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>185000</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/HeroLevelConfig.xlsx
+++ b/Configs/GameConfig/Datas/HeroLevelConfig.xlsx
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>升下一级所需经验，最高等级填0（旧 max_exp，封顶55级）</t>
+          <t>官方 Role1 经验曲线；项目最高级仍为 55，末级填 0</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
@@ -1176,7 +1176,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>160</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8">
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9">
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>200</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10">
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>300</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>400</v>
+        <v>625</v>
       </c>
     </row>
     <row r="13">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>500</v>
+        <v>675</v>
       </c>
     </row>
     <row r="14">
@@ -1302,7 +1302,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>600</v>
+        <v>725</v>
       </c>
     </row>
     <row r="15">
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>700</v>
+        <v>775</v>
       </c>
     </row>
     <row r="16">
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>825</v>
       </c>
     </row>
     <row r="17">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>900</v>
+        <v>875</v>
       </c>
     </row>
     <row r="18">
@@ -1374,7 +1374,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1200</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="19">
@@ -1392,7 +1392,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1400</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="20">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1600</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="21">
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2000</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="22">
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2400</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="23">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3000</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="24">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="25">
